--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,456 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121981142</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100288</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598259</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6679556</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flertalet!</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121981194</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100288</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598283</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6679577</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flertalet!</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121981136</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91343</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598259</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6679556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121981181</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91343</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598283</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6679577</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981142</v>
+        <v>121981136</v>
       </c>
       <c r="B4" t="n">
-        <v>100288</v>
+        <v>91343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,27 +933,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1001,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121981194</v>
+        <v>121981181</v>
       </c>
       <c r="B5" t="n">
-        <v>100288</v>
+        <v>91343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,27 +1048,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1113,7 +1115,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981136</v>
+        <v>121981142</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>100288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,30 +1159,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981181</v>
+        <v>121981194</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>100288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,26 +1271,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981136</v>
+        <v>121981181</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,11 +950,7 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -964,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R4" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121981181</v>
+        <v>121981194</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>100306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,26 +1044,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,7 +1112,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,7 +1143,7 @@
         <v>121981142</v>
       </c>
       <c r="B6" t="n">
-        <v>100288</v>
+        <v>100306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1255,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981194</v>
+        <v>121981136</v>
       </c>
       <c r="B7" t="n">
-        <v>100288</v>
+        <v>91357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,27 +1268,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R7" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981136</v>
+        <v>121981142</v>
       </c>
       <c r="B4" t="n">
-        <v>91394</v>
+        <v>100350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,30 +933,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1004,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1143,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981142</v>
+        <v>121981194</v>
       </c>
       <c r="B6" t="n">
         <v>100350</v>
@@ -1187,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R6" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1255,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981194</v>
+        <v>121981136</v>
       </c>
       <c r="B7" t="n">
-        <v>100350</v>
+        <v>91394</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,27 +1268,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R7" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981142</v>
+        <v>121981194</v>
       </c>
       <c r="B4" t="n">
-        <v>100350</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R4" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121981181</v>
+        <v>121981136</v>
       </c>
       <c r="B5" t="n">
-        <v>91394</v>
+        <v>91404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,7 +1062,11 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1072,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R5" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981194</v>
+        <v>121981181</v>
       </c>
       <c r="B6" t="n">
-        <v>100350</v>
+        <v>91404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,27 +1160,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1224,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981136</v>
+        <v>121981142</v>
       </c>
       <c r="B7" t="n">
-        <v>91394</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,30 +1271,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981194</v>
+        <v>121981142</v>
       </c>
       <c r="B4" t="n">
         <v>100360</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R4" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121981136</v>
+        <v>121981181</v>
       </c>
       <c r="B5" t="n">
         <v>91404</v>
@@ -1062,11 +1062,7 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1076,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R5" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981181</v>
+        <v>121981136</v>
       </c>
       <c r="B6" t="n">
         <v>91404</v>
@@ -1177,7 +1173,11 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R6" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera på lågorna men allt är planerad för avverkning inom reservatet vilket är en naturvårdsskandal!! Varför har Länsstyrelsen så klen naturvårdskompetens?!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981142</v>
+        <v>121981194</v>
       </c>
       <c r="B7" t="n">
         <v>100360</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R7" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981142</v>
+        <v>121981194</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>100372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598259</v>
+        <v>598283</v>
       </c>
       <c r="R4" t="n">
-        <v>6679556</v>
+        <v>6679577</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1032,7 +1032,7 @@
         <v>121981181</v>
       </c>
       <c r="B5" t="n">
-        <v>91404</v>
+        <v>91416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981136</v>
+        <v>121981142</v>
       </c>
       <c r="B6" t="n">
-        <v>91404</v>
+        <v>100372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,30 +1156,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,7 +1224,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>Flertalet!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981194</v>
+        <v>121981136</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>91416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,27 +1268,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598283</v>
+        <v>598259</v>
       </c>
       <c r="R7" t="n">
-        <v>6679577</v>
+        <v>6679556</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598320.1486303252</v>
+        <v>598320</v>
       </c>
       <c r="R2" t="n">
-        <v>6679586.362065972</v>
+        <v>6679586</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2000-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92828851</v>
       </c>
       <c r="B2" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92828851</v>
+        <v>421562</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>80335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strandskinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium rivulare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Mont.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hamre g:la tomt, v om Hamreheden., Gstr</t>
+          <t>Mälholmen, Hamre i Irstamyren, 6 km SSV Österfärnebo k:a., Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598320</v>
+        <v>598152</v>
       </c>
       <c r="R2" t="n">
-        <v>6679586</v>
+        <v>6679584</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-07-11</t>
+          <t>1993-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-07-11</t>
+          <t>1993-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,77 +759,80 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skog, Granskog, tät, planterad, med små luckor, på gammal frisk, näringsrik torpmark intill väg.</t>
+          <t>Populus (1 träd) i kantzonen mot granplantering.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 206444L</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Sundström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97604640</v>
+        <v>121981136</v>
       </c>
       <c r="B3" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ista naturreservat, Gstr</t>
+          <t>Ista Naturreservat , Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598190.2390643335</v>
+        <v>598259</v>
       </c>
       <c r="R3" t="n">
-        <v>6679531.694814997</v>
+        <v>6679556</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,22 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,37 +878,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121981194</v>
+        <v>121981164</v>
       </c>
       <c r="B4" t="n">
-        <v>100372</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,27 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598283</v>
+        <v>598260</v>
       </c>
       <c r="R4" t="n">
-        <v>6679577</v>
+        <v>6679424</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +975,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flertalet!</t>
+          <t>Flera och allt skall huggas inom reservatet!!?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,12 +1006,7 @@
         <v>121981181</v>
       </c>
       <c r="B5" t="n">
-        <v>91416</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,54 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121981142</v>
+        <v>97604640</v>
       </c>
       <c r="B6" t="n">
-        <v>100372</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>2014</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ista Naturreservat , Gstr</t>
+          <t>Ista naturreservat, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598259</v>
+        <v>598190</v>
       </c>
       <c r="R6" t="n">
-        <v>6679556</v>
+        <v>6679531</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,17 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flertalet!</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,34 +1188,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121981136</v>
+        <v>97604639</v>
       </c>
       <c r="B7" t="n">
-        <v>91416</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,41 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ista Naturreservat , Gstr</t>
+          <t>Ista naturreservat, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598259</v>
+        <v>598149</v>
       </c>
       <c r="R7" t="n">
-        <v>6679556</v>
+        <v>6679581</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig med död ved och flertalet fynd av brandticka och även svart trolldruva i den äldre och produktiva granskogar inom naturreservatet men allt är planerad för avverkning!!?? Men hallå, naturreservat och naturvårdsarter plus en massa död ved, varför skall det här kallhuggas?? Inkompetent Länsstyrelse eller!?</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,22 +1289,350 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>92828851</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hamre g:la tomt, v om Hamreheden., Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6679586</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2000-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2000-07-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>skog, Granskog, tät, planterad, med små luckor, på gammal frisk, näringsrik torpmark intill väg.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 206444L</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Sundström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121981142</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>598259</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6679556</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flertalet!</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121981194</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ista Naturreservat , Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>598283</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6679577</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flertalet!</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24802-2023 artfynd.xlsx
+++ b/artfynd/A 24802-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/421562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981181</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604640</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97604639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92828851</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981142</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,8 +1678,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121981194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>